--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-Next-80B-A3B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,22 +420,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.1604938271604938</v>
+        <v>0.1728395061728395</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.2773722627737226</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="D2">
-        <v>0.8839285714285714</v>
+        <v>0.8761061946902655</v>
       </c>
       <c r="E2">
         <v>81</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2">
         <v>25</v>
